--- a/output_tcc_var/tabelas/02_diagnosticos_residuos.xlsx
+++ b/output_tcc_var/tabelas/02_diagnosticos_residuos.xlsx
@@ -460,16 +460,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01417126146113486</v>
+        <v>0.1577378048527049</v>
       </c>
       <c r="D2" t="n">
-        <v>3.316752836032891e-29</v>
+        <v>7.685830407987689e-25</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01574528391188202</v>
+        <v>0.237113876735982</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02666013782106718</v>
+        <v>0.3464337416030946</v>
       </c>
     </row>
     <row r="3">
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.01417126146113486</v>
+        <v>0.1577378048527049</v>
       </c>
       <c r="D3" t="n">
-        <v>3.316752836032891e-29</v>
+        <v>7.685830407987689e-25</v>
       </c>
       <c r="E3" t="n">
-        <v>0.282965344827358</v>
+        <v>0.1566888340180164</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3659835531741715</v>
+        <v>0.2469506747906672</v>
       </c>
     </row>
     <row r="4">
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.01417126146113486</v>
+        <v>0.1577378048527049</v>
       </c>
       <c r="D4" t="n">
-        <v>3.316752836032891e-29</v>
+        <v>7.685830407987689e-25</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01452044938628471</v>
+        <v>0.16298373981713</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02469738369582895</v>
+        <v>0.2551149152477379</v>
       </c>
     </row>
     <row r="5">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.01417126146113486</v>
+        <v>0.1577378048527049</v>
       </c>
       <c r="D5" t="n">
-        <v>3.316752836032891e-29</v>
+        <v>7.685830407987689e-25</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09205285946020419</v>
+        <v>0.01969934524520968</v>
       </c>
       <c r="F5" t="n">
-        <v>0.136153389333593</v>
+        <v>0.04140605249967486</v>
       </c>
     </row>
     <row r="6">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05673559321682474</v>
+        <v>0.05673022534868926</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0189976453253224</v>
+        <v>0.01899698307715606</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02833407939967425</v>
+        <v>0.02833312709395027</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.05673559321682474</v>
+        <v>0.05673022534868926</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05124396096899844</v>
+        <v>0.05124092681742299</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07299364942054404</v>
+        <v>0.07298957597472036</v>
       </c>
     </row>
     <row r="8">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.05673559321682474</v>
+        <v>0.05673022534868926</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3197576952781113</v>
+        <v>0.3197679546621427</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3901153203838686</v>
+        <v>0.3901263378103111</v>
       </c>
     </row>
     <row r="9">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.05673559321682474</v>
+        <v>0.05673022534868926</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4000519391520223</v>
+        <v>0.3996695891561866</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4744776269868159</v>
+        <v>0.4740843839465964</v>
       </c>
     </row>
     <row r="10">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4202634781949482</v>
+        <v>0.4202710699964833</v>
       </c>
       <c r="D10" t="n">
-        <v>4.50610312117055e-24</v>
+        <v>4.51119109628854e-24</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01666978649589851</v>
+        <v>0.01667043005623128</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02497473032640947</v>
+        <v>0.0249756624383662</v>
       </c>
     </row>
     <row r="11">
@@ -676,16 +676,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.4202634781949482</v>
+        <v>0.4202710699964833</v>
       </c>
       <c r="D11" t="n">
-        <v>4.50610312117055e-24</v>
+        <v>4.51119109628854e-24</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03083726267184438</v>
+        <v>0.03083758103359741</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04509202276400405</v>
+        <v>0.04509246691859131</v>
       </c>
     </row>
     <row r="12">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.4202634781949482</v>
+        <v>0.4202710699964833</v>
       </c>
       <c r="D12" t="n">
-        <v>4.50610312117055e-24</v>
+        <v>4.51119109628854e-24</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1917090996068656</v>
+        <v>0.1917095586938116</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2471376506232453</v>
+        <v>0.2471381851441115</v>
       </c>
     </row>
     <row r="13">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4202634781949482</v>
+        <v>0.4202710699964833</v>
       </c>
       <c r="D13" t="n">
-        <v>4.50610312117055e-24</v>
+        <v>4.51119109628854e-24</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4057943828548606</v>
+        <v>0.4054019009600385</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4803743003942393</v>
+        <v>0.4799718353881514</v>
       </c>
     </row>
     <row r="14">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2591100711119333</v>
+        <v>0.2590827076644028</v>
       </c>
       <c r="D14" t="n">
-        <v>2.304289334742178e-194</v>
+        <v>2.261045748033938e-194</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02328977527293836</v>
+        <v>0.02329025007421499</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03446843752847446</v>
+        <v>0.03446911213185153</v>
       </c>
     </row>
     <row r="15">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2591100711119333</v>
+        <v>0.2590827076644028</v>
       </c>
       <c r="D15" t="n">
-        <v>2.304289334742178e-194</v>
+        <v>2.261045748033938e-194</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0453784567339045</v>
+        <v>0.04537673754646507</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06508052493530443</v>
+        <v>0.06507819396595621</v>
       </c>
     </row>
     <row r="16">
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.2591100711119333</v>
+        <v>0.2590827076644028</v>
       </c>
       <c r="D16" t="n">
-        <v>2.304289334742178e-194</v>
+        <v>2.261045748033938e-194</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02255014042913826</v>
+        <v>0.022547693045336</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03341652198242469</v>
+        <v>0.03341303783726238</v>
       </c>
     </row>
     <row r="17">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.2591100711119333</v>
+        <v>0.2590827076644028</v>
       </c>
       <c r="D17" t="n">
-        <v>2.304289334742178e-194</v>
+        <v>2.261045748033938e-194</v>
       </c>
       <c r="E17" t="n">
-        <v>0.48179027633675</v>
+        <v>0.4813630228893971</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5568068106847196</v>
+        <v>0.556385214493909</v>
       </c>
     </row>
     <row r="18">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.05209954142698507</v>
+        <v>0.05657013815859209</v>
       </c>
       <c r="D18" t="n">
-        <v>2.425291584032053e-49</v>
+        <v>1.377799607955502e-64</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02196445835995032</v>
+        <v>0.01913314671295476</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03645559224590076</v>
+        <v>0.03202916130765257</v>
       </c>
     </row>
     <row r="19">
@@ -868,16 +868,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.05209954142698507</v>
+        <v>0.05657013815859209</v>
       </c>
       <c r="D19" t="n">
-        <v>2.425291584032053e-49</v>
+        <v>1.377799607955502e-64</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2460782779829187</v>
+        <v>0.2584505913351031</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3245554566431028</v>
+        <v>0.3385795383160589</v>
       </c>
     </row>
     <row r="20">
@@ -892,16 +892,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.05209954142698507</v>
+        <v>0.05657013815859209</v>
       </c>
       <c r="D20" t="n">
-        <v>2.425291584032053e-49</v>
+        <v>1.377799607955502e-64</v>
       </c>
       <c r="E20" t="n">
-        <v>0.004251803117110679</v>
+        <v>0.01732276975648651</v>
       </c>
       <c r="F20" t="n">
-        <v>0.007625738226414962</v>
+        <v>0.02917058600961464</v>
       </c>
     </row>
     <row r="21">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.05209954142698507</v>
+        <v>0.05657013815859209</v>
       </c>
       <c r="D21" t="n">
-        <v>2.425291584032053e-49</v>
+        <v>1.377799607955502e-64</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5021242597664508</v>
+        <v>0.5230379748388523</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5920326779239384</v>
+        <v>0.6120580409297804</v>
       </c>
     </row>
     <row r="22">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.3952197400998829</v>
+        <v>0.3952197400998324</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.02658088968779822</v>
+        <v>0.02658088968779992</v>
       </c>
       <c r="F22" t="n">
-        <v>0.04356967362797885</v>
+        <v>0.04356967362798108</v>
       </c>
     </row>
     <row r="23">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.3952197400998829</v>
+        <v>0.3952197400998324</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6202835997072171</v>
+        <v>0.6202835997072198</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7020163641919033</v>
+        <v>0.7020163641919104</v>
       </c>
     </row>
     <row r="24">
@@ -988,16 +988,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.3952197400998829</v>
+        <v>0.3952197400998324</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.419346866972318</v>
+        <v>0.4193468669722807</v>
       </c>
       <c r="F24" t="n">
-        <v>0.510285913518384</v>
+        <v>0.5102859135183517</v>
       </c>
     </row>
     <row r="25">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.3952197400998829</v>
+        <v>0.3952197400998324</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7598861409861776</v>
+        <v>0.759886140986117</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8222968401066245</v>
+        <v>0.8222968401065758</v>
       </c>
     </row>
     <row r="26">
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.1631685042720686</v>
+        <v>0.1631685042720763</v>
       </c>
       <c r="D26" t="n">
-        <v>1.265109057193923e-114</v>
+        <v>1.265109057170104e-114</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02091608524006513</v>
+        <v>0.02091608524006407</v>
       </c>
       <c r="F26" t="n">
-        <v>0.03108505893316965</v>
+        <v>0.03108505893316853</v>
       </c>
     </row>
     <row r="27">
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.1631685042720686</v>
+        <v>0.1631685042720763</v>
       </c>
       <c r="D27" t="n">
-        <v>1.265109057193923e-114</v>
+        <v>1.265109057170104e-114</v>
       </c>
       <c r="E27" t="n">
         <v>0.03696087289130555</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05357947139169156</v>
+        <v>0.05357947139169093</v>
       </c>
     </row>
     <row r="28">
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1631685042720686</v>
+        <v>0.1631685042720763</v>
       </c>
       <c r="D28" t="n">
-        <v>1.265109057193923e-114</v>
+        <v>1.265109057170104e-114</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1684010172479887</v>
+        <v>0.1684010172479737</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2197630522315623</v>
+        <v>0.2197630522315486</v>
       </c>
     </row>
     <row r="29">
@@ -1108,16 +1108,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.1631685042720686</v>
+        <v>0.1631685042720763</v>
       </c>
       <c r="D29" t="n">
-        <v>1.265109057193923e-114</v>
+        <v>1.265109057170104e-114</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7699045571587837</v>
+        <v>0.7699045571587863</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8214469559758489</v>
+        <v>0.8214469559758516</v>
       </c>
     </row>
     <row r="30">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1775560467012555</v>
+        <v>0.1775560467012756</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1156,16 +1156,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1775560467012555</v>
+        <v>0.1775560467012756</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.04444386961128986</v>
+        <v>0.04444386961129027</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06381232059856511</v>
+        <v>0.0638123205985654</v>
       </c>
     </row>
     <row r="32">
@@ -1180,16 +1180,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1775560467012555</v>
+        <v>0.1775560467012756</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.02078362771294175</v>
+        <v>0.02078362771294041</v>
       </c>
       <c r="F32" t="n">
-        <v>0.03089560554422906</v>
+        <v>0.03089560554422713</v>
       </c>
     </row>
     <row r="33">
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1775560467012555</v>
+        <v>0.1775560467012756</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         <v>0.7695600044214151</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8211540317702886</v>
+        <v>0.8211540317702949</v>
       </c>
     </row>
   </sheetData>
